--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-08-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B61ADDF-0AF3-46DD-B8AF-213AA8F235CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5DF0C9-84FC-4340-8FCA-C109A1E63798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="2565" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34965" yWindow="1635" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="379">
   <si>
     <t>SKU</t>
   </si>
@@ -613,9 +613,6 @@
     <t>£74.68</t>
   </si>
   <si>
-    <t>£68.2</t>
-  </si>
-  <si>
     <t>£61.88</t>
   </si>
   <si>
@@ -646,9 +643,6 @@
     <t>£1335.44</t>
   </si>
   <si>
-    <t>£1233.8</t>
-  </si>
-  <si>
     <t>£1079.88</t>
   </si>
   <si>
@@ -685,9 +679,6 @@
     <t>£1619.78</t>
   </si>
   <si>
-    <t>£1504.9</t>
-  </si>
-  <si>
     <t>£1302.0</t>
   </si>
   <si>
@@ -760,9 +751,6 @@
     <t>£64.38</t>
   </si>
   <si>
-    <t>£71.04</t>
-  </si>
-  <si>
     <t>£51.95</t>
   </si>
   <si>
@@ -796,9 +784,6 @@
     <t>£72.69</t>
   </si>
   <si>
-    <t>£95.5</t>
-  </si>
-  <si>
     <t>£55.65</t>
   </si>
   <si>
@@ -829,9 +814,6 @@
     <t>£75.76</t>
   </si>
   <si>
-    <t>£84.22</t>
-  </si>
-  <si>
     <t>£60.99</t>
   </si>
   <si>
@@ -985,9 +967,6 @@
     <t>£2208.32</t>
   </si>
   <si>
-    <t>£107.07</t>
-  </si>
-  <si>
     <t>£1727.84</t>
   </si>
   <si>
@@ -1021,9 +1000,6 @@
     <t>£2057.12</t>
   </si>
   <si>
-    <t>£148.27</t>
-  </si>
-  <si>
     <t>£1996.64</t>
   </si>
   <si>
@@ -1057,9 +1033,6 @@
     <t>£2183.04</t>
   </si>
   <si>
-    <t>£165.97</t>
-  </si>
-  <si>
     <t>£1972.64</t>
   </si>
   <si>
@@ -1069,48 +1042,9 @@
     <t>£2265.12</t>
   </si>
   <si>
-    <t>£18.00</t>
-  </si>
-  <si>
-    <t>£22.50</t>
-  </si>
-  <si>
-    <t>£23.50</t>
-  </si>
-  <si>
     <t>£30.00</t>
   </si>
   <si>
-    <t>£33.00</t>
-  </si>
-  <si>
-    <t>£36.75</t>
-  </si>
-  <si>
-    <t>£40.50</t>
-  </si>
-  <si>
-    <t>£40.00</t>
-  </si>
-  <si>
-    <t>£49.25</t>
-  </si>
-  <si>
-    <t>£49.75</t>
-  </si>
-  <si>
-    <t>£59.75</t>
-  </si>
-  <si>
-    <t>£60.75</t>
-  </si>
-  <si>
-    <t>£1,080.00</t>
-  </si>
-  <si>
-    <t>£1,325.00</t>
-  </si>
-  <si>
     <t>£51.75</t>
   </si>
   <si>
@@ -1163,6 +1097,66 @@
   </si>
   <si>
     <t>£91.54</t>
+  </si>
+  <si>
+    <t>£14.25</t>
+  </si>
+  <si>
+    <t>£17.50</t>
+  </si>
+  <si>
+    <t>£21.25</t>
+  </si>
+  <si>
+    <t>£23.00</t>
+  </si>
+  <si>
+    <t>£29.50</t>
+  </si>
+  <si>
+    <t>£32.50</t>
+  </si>
+  <si>
+    <t>£36.00</t>
+  </si>
+  <si>
+    <t>£39.50</t>
+  </si>
+  <si>
+    <t>£48.50</t>
+  </si>
+  <si>
+    <t>£49.00</t>
+  </si>
+  <si>
+    <t>£60.00</t>
+  </si>
+  <si>
+    <t>£59.25</t>
+  </si>
+  <si>
+    <t>£1,295.00</t>
+  </si>
+  <si>
+    <t>£68.20</t>
+  </si>
+  <si>
+    <t>£1233.84</t>
+  </si>
+  <si>
+    <t>£1504.92</t>
+  </si>
+  <si>
+    <t>£63.17</t>
+  </si>
+  <si>
+    <t>£1713.12</t>
+  </si>
+  <si>
+    <t>£2372.32</t>
+  </si>
+  <si>
+    <t>£2655.52</t>
   </si>
 </sst>
 </file>
@@ -1601,7 +1595,7 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>359</v>
       </c>
       <c r="G2" t="s">
         <v>22</v>
@@ -1657,7 +1651,7 @@
         <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="G3" t="s">
         <v>36</v>
@@ -1669,7 +1663,7 @@
         <v>38</v>
       </c>
       <c r="J3" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="K3" t="s">
         <v>39</v>
@@ -1713,7 +1707,7 @@
         <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="G4" t="s">
         <v>47</v>
@@ -1769,7 +1763,7 @@
         <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="G5" t="s">
         <v>60</v>
@@ -1825,7 +1819,7 @@
         <v>72</v>
       </c>
       <c r="F6" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="G6" t="s">
         <v>73</v>
@@ -1881,7 +1875,7 @@
         <v>85</v>
       </c>
       <c r="F7" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="G7" t="s">
         <v>86</v>
@@ -1893,7 +1887,7 @@
         <v>88</v>
       </c>
       <c r="J7" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="K7" t="s">
         <v>89</v>
@@ -1937,7 +1931,7 @@
         <v>97</v>
       </c>
       <c r="F8" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="G8" t="s">
         <v>98</v>
@@ -1993,7 +1987,7 @@
         <v>109</v>
       </c>
       <c r="F9" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="G9" t="s">
         <v>110</v>
@@ -2049,7 +2043,7 @@
         <v>120</v>
       </c>
       <c r="F10" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="G10" t="s">
         <v>121</v>
@@ -2061,7 +2055,7 @@
         <v>123</v>
       </c>
       <c r="J10" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="K10" t="s">
         <v>124</v>
@@ -2105,7 +2099,7 @@
         <v>133</v>
       </c>
       <c r="F11" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="G11" t="s">
         <v>133</v>
@@ -2161,7 +2155,7 @@
         <v>144</v>
       </c>
       <c r="F12" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="G12" t="s">
         <v>145</v>
@@ -2217,7 +2211,7 @@
         <v>157</v>
       </c>
       <c r="F13" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="G13" t="s">
         <v>158</v>
@@ -2229,7 +2223,7 @@
         <v>160</v>
       </c>
       <c r="J13" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
       <c r="K13" t="s">
         <v>161</v>
@@ -2273,7 +2267,7 @@
         <v>169</v>
       </c>
       <c r="F14" t="s">
-        <v>359</v>
+        <v>174</v>
       </c>
       <c r="G14" t="s">
         <v>170</v>
@@ -2285,7 +2279,7 @@
         <v>172</v>
       </c>
       <c r="J14" t="s">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="K14" t="s">
         <v>173</v>
@@ -2329,7 +2323,7 @@
         <v>146</v>
       </c>
       <c r="F15" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="G15" t="s">
         <v>181</v>
@@ -2385,7 +2379,7 @@
         <v>191</v>
       </c>
       <c r="F16" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="G16" t="s">
         <v>192</v>
@@ -2397,7 +2391,7 @@
         <v>194</v>
       </c>
       <c r="J16" t="s">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="K16" t="s">
         <v>195</v>
@@ -2409,72 +2403,72 @@
         <v>196</v>
       </c>
       <c r="N16" t="s">
-        <v>197</v>
+        <v>372</v>
       </c>
       <c r="O16" t="s">
         <v>191</v>
       </c>
       <c r="P16" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q16" t="s">
         <v>198</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R16" t="s">
         <v>199</v>
-      </c>
-      <c r="R16" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>200</v>
+      </c>
+      <c r="B17" t="s">
         <v>201</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>202</v>
       </c>
-      <c r="C17" t="s">
-        <v>203</v>
-      </c>
       <c r="D17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F17" t="s">
-        <v>361</v>
+        <v>202</v>
       </c>
       <c r="G17" t="s">
         <v>146</v>
       </c>
       <c r="H17" t="s">
+        <v>203</v>
+      </c>
+      <c r="I17" t="s">
         <v>204</v>
-      </c>
-      <c r="I17" t="s">
-        <v>205</v>
       </c>
       <c r="J17" t="s">
         <v>146</v>
       </c>
       <c r="K17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L17" t="s">
         <v>146</v>
       </c>
       <c r="M17" t="s">
+        <v>206</v>
+      </c>
+      <c r="N17" t="s">
+        <v>373</v>
+      </c>
+      <c r="O17" t="s">
         <v>207</v>
       </c>
-      <c r="N17" t="s">
+      <c r="P17" t="s">
         <v>208</v>
       </c>
-      <c r="O17" t="s">
+      <c r="Q17" t="s">
         <v>209</v>
-      </c>
-      <c r="P17" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>211</v>
       </c>
       <c r="R17" t="s">
         <v>146</v>
@@ -2482,234 +2476,234 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" t="s">
+        <v>211</v>
+      </c>
+      <c r="C18" t="s">
         <v>212</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
+        <v>212</v>
+      </c>
+      <c r="E18" t="s">
+        <v>212</v>
+      </c>
+      <c r="F18" t="s">
+        <v>371</v>
+      </c>
+      <c r="G18" t="s">
         <v>213</v>
       </c>
-      <c r="C18" t="s">
+      <c r="H18" t="s">
         <v>214</v>
       </c>
-      <c r="D18" t="s">
-        <v>214</v>
-      </c>
-      <c r="E18" t="s">
-        <v>214</v>
-      </c>
-      <c r="F18" t="s">
-        <v>362</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>215</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J18" t="s">
         <v>216</v>
       </c>
-      <c r="I18" t="s">
+      <c r="K18" t="s">
         <v>217</v>
-      </c>
-      <c r="J18" t="s">
-        <v>218</v>
-      </c>
-      <c r="K18" t="s">
-        <v>219</v>
       </c>
       <c r="L18" t="s">
         <v>146</v>
       </c>
       <c r="M18" t="s">
+        <v>218</v>
+      </c>
+      <c r="N18" t="s">
+        <v>374</v>
+      </c>
+      <c r="O18" t="s">
+        <v>219</v>
+      </c>
+      <c r="P18" t="s">
         <v>220</v>
       </c>
-      <c r="N18" t="s">
+      <c r="Q18" t="s">
         <v>221</v>
       </c>
-      <c r="O18" t="s">
+      <c r="R18" t="s">
         <v>222</v>
-      </c>
-      <c r="P18" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>224</v>
-      </c>
-      <c r="R18" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B19" t="s">
+        <v>224</v>
+      </c>
+      <c r="C19" t="s">
+        <v>225</v>
+      </c>
+      <c r="D19" t="s">
+        <v>225</v>
+      </c>
+      <c r="E19" t="s">
+        <v>225</v>
+      </c>
+      <c r="F19" t="s">
+        <v>341</v>
+      </c>
+      <c r="G19" t="s">
         <v>226</v>
       </c>
-      <c r="B19" t="s">
+      <c r="H19" t="s">
         <v>227</v>
       </c>
-      <c r="C19" t="s">
+      <c r="I19" t="s">
         <v>228</v>
       </c>
-      <c r="D19" t="s">
-        <v>228</v>
-      </c>
-      <c r="E19" t="s">
-        <v>228</v>
-      </c>
-      <c r="F19" t="s">
-        <v>363</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="J19" t="s">
         <v>229</v>
       </c>
-      <c r="H19" t="s">
+      <c r="K19" t="s">
         <v>230</v>
-      </c>
-      <c r="I19" t="s">
-        <v>231</v>
-      </c>
-      <c r="J19" t="s">
-        <v>232</v>
-      </c>
-      <c r="K19" t="s">
-        <v>233</v>
       </c>
       <c r="L19" t="s">
         <v>21</v>
       </c>
       <c r="M19" t="s">
+        <v>231</v>
+      </c>
+      <c r="N19" t="s">
+        <v>232</v>
+      </c>
+      <c r="O19" t="s">
+        <v>225</v>
+      </c>
+      <c r="P19" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q19" t="s">
         <v>234</v>
       </c>
-      <c r="N19" t="s">
+      <c r="R19" t="s">
         <v>235</v>
-      </c>
-      <c r="O19" t="s">
-        <v>228</v>
-      </c>
-      <c r="P19" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>237</v>
-      </c>
-      <c r="R19" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>236</v>
+      </c>
+      <c r="B20" t="s">
+        <v>237</v>
+      </c>
+      <c r="C20" t="s">
+        <v>238</v>
+      </c>
+      <c r="D20" t="s">
+        <v>238</v>
+      </c>
+      <c r="E20" t="s">
+        <v>238</v>
+      </c>
+      <c r="F20" t="s">
+        <v>342</v>
+      </c>
+      <c r="G20" t="s">
         <v>239</v>
       </c>
-      <c r="B20" t="s">
+      <c r="H20" t="s">
         <v>240</v>
-      </c>
-      <c r="C20" t="s">
-        <v>241</v>
-      </c>
-      <c r="D20" t="s">
-        <v>241</v>
-      </c>
-      <c r="E20" t="s">
-        <v>241</v>
-      </c>
-      <c r="F20" t="s">
-        <v>364</v>
-      </c>
-      <c r="G20" t="s">
-        <v>242</v>
-      </c>
-      <c r="H20" t="s">
-        <v>243</v>
       </c>
       <c r="I20" t="s">
         <v>183</v>
       </c>
       <c r="J20" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="K20" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="L20" t="s">
         <v>21</v>
       </c>
       <c r="M20" t="s">
+        <v>242</v>
+      </c>
+      <c r="N20" t="s">
+        <v>232</v>
+      </c>
+      <c r="O20" t="s">
+        <v>243</v>
+      </c>
+      <c r="P20" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>238</v>
+      </c>
+      <c r="R20" t="s">
         <v>245</v>
-      </c>
-      <c r="N20" t="s">
-        <v>246</v>
-      </c>
-      <c r="O20" t="s">
-        <v>247</v>
-      </c>
-      <c r="P20" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>241</v>
-      </c>
-      <c r="R20" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>246</v>
+      </c>
+      <c r="B21" t="s">
+        <v>247</v>
+      </c>
+      <c r="C21" t="s">
+        <v>248</v>
+      </c>
+      <c r="D21" t="s">
+        <v>248</v>
+      </c>
+      <c r="E21" t="s">
+        <v>248</v>
+      </c>
+      <c r="F21" t="s">
+        <v>343</v>
+      </c>
+      <c r="G21" t="s">
+        <v>249</v>
+      </c>
+      <c r="H21" t="s">
         <v>250</v>
       </c>
-      <c r="B21" t="s">
+      <c r="I21" t="s">
         <v>251</v>
       </c>
-      <c r="C21" t="s">
+      <c r="J21" t="s">
+        <v>356</v>
+      </c>
+      <c r="K21" t="s">
         <v>252</v>
-      </c>
-      <c r="D21" t="s">
-        <v>252</v>
-      </c>
-      <c r="E21" t="s">
-        <v>252</v>
-      </c>
-      <c r="F21" t="s">
-        <v>365</v>
-      </c>
-      <c r="G21" t="s">
-        <v>253</v>
-      </c>
-      <c r="H21" t="s">
-        <v>254</v>
-      </c>
-      <c r="I21" t="s">
-        <v>255</v>
-      </c>
-      <c r="J21" t="s">
-        <v>378</v>
-      </c>
-      <c r="K21" t="s">
-        <v>256</v>
       </c>
       <c r="L21" t="s">
         <v>21</v>
       </c>
       <c r="M21" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="N21" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="O21" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="P21" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="Q21" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="R21" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B22" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C22" t="s">
         <v>181</v>
@@ -2721,119 +2715,119 @@
         <v>181</v>
       </c>
       <c r="F22" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="G22" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="H22" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="I22" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="J22" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="K22" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="L22" t="s">
         <v>21</v>
       </c>
       <c r="M22" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="N22" t="s">
-        <v>269</v>
+        <v>375</v>
       </c>
       <c r="O22" t="s">
         <v>181</v>
       </c>
       <c r="P22" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="Q22" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="R22" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B23" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C23" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D23" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E23" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="F23" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="G23" t="s">
         <v>146</v>
       </c>
       <c r="H23" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="I23" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="J23" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="K23" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="L23" t="s">
         <v>21</v>
       </c>
       <c r="M23" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="N23" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="O23" t="s">
+        <v>269</v>
+      </c>
+      <c r="P23" t="s">
         <v>275</v>
       </c>
-      <c r="P23" t="s">
-        <v>281</v>
-      </c>
       <c r="Q23" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="R23" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B24" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C24" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E24" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="F24" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="G24" t="s">
         <v>146</v>
@@ -2842,51 +2836,51 @@
         <v>178</v>
       </c>
       <c r="I24" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="J24" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="K24" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="L24" t="s">
         <v>21</v>
       </c>
       <c r="M24" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="N24" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="O24" t="s">
+        <v>280</v>
+      </c>
+      <c r="P24" t="s">
         <v>286</v>
       </c>
-      <c r="P24" t="s">
-        <v>292</v>
-      </c>
       <c r="Q24" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="R24" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B25" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C25" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="D25" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E25" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="F25" t="s">
         <v>146</v>
@@ -2901,7 +2895,7 @@
         <v>146</v>
       </c>
       <c r="J25" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="K25" t="s">
         <v>146</v>
@@ -2910,13 +2904,13 @@
         <v>146</v>
       </c>
       <c r="M25" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="N25" t="s">
         <v>160</v>
       </c>
       <c r="O25" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="P25" t="s">
         <v>146</v>
@@ -2930,226 +2924,226 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B26" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C26" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="D26" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E26" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="F26" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="G26" t="s">
         <v>146</v>
       </c>
       <c r="H26" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I26" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J26" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="K26" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="L26" t="s">
         <v>21</v>
       </c>
       <c r="M26" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="N26" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="O26" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="P26" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="Q26" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="R26" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B27" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C27" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D27" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="E27" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F27" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="G27" t="s">
         <v>146</v>
       </c>
       <c r="H27" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="I27" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="J27" t="s">
         <v>146</v>
       </c>
       <c r="K27" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="L27" t="s">
         <v>21</v>
       </c>
       <c r="M27" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="N27" t="s">
-        <v>321</v>
+        <v>376</v>
       </c>
       <c r="O27" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="P27" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="Q27" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="R27" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B28" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C28" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="D28" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="E28" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F28" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="G28" t="s">
         <v>146</v>
       </c>
       <c r="H28" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="I28" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="J28" t="s">
         <v>146</v>
       </c>
       <c r="K28" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="L28" t="s">
         <v>21</v>
       </c>
       <c r="M28" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="N28" t="s">
-        <v>333</v>
+        <v>377</v>
       </c>
       <c r="O28" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="P28" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="Q28" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="R28" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="B29" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C29" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="D29" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="E29" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F29" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="G29" t="s">
         <v>146</v>
       </c>
       <c r="H29" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I29" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="J29" t="s">
         <v>146</v>
       </c>
       <c r="K29" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="L29" t="s">
         <v>146</v>
       </c>
       <c r="M29" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="N29" t="s">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="O29" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="P29" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="Q29" t="s">
         <v>146</v>
       </c>
       <c r="R29" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
